--- a/data/trans_orig/IP07A13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45858</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>27700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41759</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39888</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45991</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61169</t>
+          <t>60366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46443</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63208</t>
+          <t>62945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84438</t>
+          <t>85337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>33143</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48030</t>
+          <t>47462</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37802</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53176</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76364</t>
+          <t>75447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97460</t>
+          <t>97686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28296</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35559</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>60154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>31340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>41164</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>68715</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>21047</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28325</t>
+          <t>28551</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>13930</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34643</t>
+          <t>34530</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49113</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>100614</t>
+          <t>101159</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>127707</t>
+          <t>127526</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>107968</t>
+          <t>108874</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>134875</t>
+          <t>135346</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>215071</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>254063</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>131806</t>
+          <t>131986</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>159291</t>
+          <t>158675</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>157956</t>
+          <t>156549</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>186472</t>
+          <t>185050</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>297618</t>
+          <t>296759</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>339056</t>
+          <t>338252</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>41931</t>
+          <t>41990</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>41955</t>
+          <t>41959</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>53428</t>
+          <t>53022</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>77390</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>27949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>45618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>33799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28785</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>41953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>31703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>34919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49410</t>
+          <t>49315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59275</t>
+          <t>60323</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81970</t>
+          <t>81483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56641</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53217</t>
+          <t>52222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>83188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>104611</t>
+          <t>104928</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33048</t>
+          <t>33418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56065</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36631</t>
+          <t>37384</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>50693</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>45812</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>73035</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93155</t>
+          <t>92542</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>21460</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>84791</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>111892</t>
+          <t>113378</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>110055</t>
+          <t>108322</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>137446</t>
+          <t>136825</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>202845</t>
+          <t>202666</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>241168</t>
+          <t>240501</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>160944</t>
+          <t>159495</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>188532</t>
+          <t>188929</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>132131</t>
+          <t>132204</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>159697</t>
+          <t>161478</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>301363</t>
+          <t>301026</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>338354</t>
+          <t>341159</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>42047</t>
+          <t>41437</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>42874</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>66588</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>46344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25646</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>36893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37177</t>
+          <t>37108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53067</t>
+          <t>53484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>20763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46349</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66870</t>
+          <t>67621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>68010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106419</t>
+          <t>104778</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129873</t>
+          <t>130340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>42139</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70417</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>95571</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>22449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>28490</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43308</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43668</t>
+          <t>43038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62587</t>
+          <t>61559</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82327</t>
+          <t>82284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39052</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56075</t>
+          <t>56236</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>39196</t>
+          <t>39099</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>24738</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>148553</t>
+          <t>148878</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>178784</t>
+          <t>179449</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>167832</t>
+          <t>167756</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>198025</t>
+          <t>198586</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>326200</t>
+          <t>325262</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>369882</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>133121</t>
+          <t>132635</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>162439</t>
+          <t>163034</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>119864</t>
+          <t>118273</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>149441</t>
+          <t>147997</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>259869</t>
+          <t>258249</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>301445</t>
+          <t>302069</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>33898</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54614</t>
+          <t>54386</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
